--- a/results/validation/gdsc_validation_of_prism_candidates.xlsx
+++ b/results/validation/gdsc_validation_of_prism_candidates.xlsx
@@ -514,10 +514,10 @@
         <v>50</v>
       </c>
       <c r="E5">
-        <v>-0.1303721488595438</v>
+        <v>-0.2212244897959184</v>
       </c>
       <c r="F5">
-        <v>0.3668373016971432</v>
+        <v>0.122605933936797</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>19</v>
       </c>
       <c r="I5">
-        <v>0.7452984026490206</v>
+        <v>0.367817801810391</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -543,10 +543,10 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>0.02865612648221344</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="F6">
-        <v>0.8967308659954059</v>
+        <v>0.6056681466311387</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -555,7 +555,7 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>0.8967308659954059</v>
+        <v>0.876292262028499</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -572,10 +572,10 @@
         <v>49</v>
       </c>
       <c r="E7">
-        <v>0.09938634367274408</v>
+        <v>0.02282508201753031</v>
       </c>
       <c r="F7">
-        <v>0.4968656017660137</v>
+        <v>0.876292262028499</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>20</v>
       </c>
       <c r="I7">
-        <v>0.7452984026490206</v>
+        <v>0.876292262028499</v>
       </c>
     </row>
   </sheetData>

--- a/results/validation/gdsc_validation_of_prism_candidates.xlsx
+++ b/results/validation/gdsc_validation_of_prism_candidates.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
   <si>
     <t>CANDIDATE</t>
   </si>
@@ -59,15 +59,6 @@
   </si>
   <si>
     <t>NOT_FOUND</t>
-  </si>
-  <si>
-    <t>DOCETAXEL (GDSC2:1007)</t>
-  </si>
-  <si>
-    <t>PACLITAXEL (GDSC1:11)</t>
-  </si>
-  <si>
-    <t>PACLITAXEL (GDSC2:1080)</t>
   </si>
   <si>
     <t>Absent from compound library</t>
@@ -457,7 +448,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -477,7 +468,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -488,16 +479,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="E4">
+        <v>-0.3793522267206478</v>
+      </c>
+      <c r="F4">
+        <v>0.01722975568031216</v>
       </c>
       <c r="G4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <v>0.03445951136062431</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -508,25 +508,25 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>-0.2212244897959184</v>
+        <v>-0.5137651821862349</v>
       </c>
       <c r="F5">
-        <v>0.122605933936797</v>
+        <v>0.0008220051984522333</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I5">
-        <v>0.367817801810391</v>
+        <v>0.003288020793808933</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -537,25 +537,25 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>0.1136363636363636</v>
+        <v>0.04360902255639097</v>
       </c>
       <c r="F6">
-        <v>0.6056681466311387</v>
+        <v>0.8551479470173744</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>0.876292262028499</v>
+        <v>0.8551479470173744</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -566,25 +566,25 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>0.02282508201753031</v>
+        <v>-0.08502024291497975</v>
       </c>
       <c r="F7">
-        <v>0.876292262028499</v>
+        <v>0.6117949873302611</v>
       </c>
       <c r="G7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I7">
-        <v>0.876292262028499</v>
+        <v>0.8157266497736814</v>
       </c>
     </row>
   </sheetData>

--- a/results/validation/gdsc_validation_of_prism_candidates.xlsx
+++ b/results/validation/gdsc_validation_of_prism_candidates.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>CANDIDATE</t>
   </si>
@@ -59,6 +59,15 @@
   </si>
   <si>
     <t>NOT_FOUND</t>
+  </si>
+  <si>
+    <t>DOCETAXEL (GDSC2:1007)</t>
+  </si>
+  <si>
+    <t>PACLITAXEL (GDSC1:11)</t>
+  </si>
+  <si>
+    <t>PACLITAXEL (GDSC2:1080)</t>
   </si>
   <si>
     <t>Absent from compound library</t>
@@ -448,7 +457,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -468,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -479,25 +488,16 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>39</v>
-      </c>
-      <c r="E4">
-        <v>-0.3793522267206478</v>
-      </c>
-      <c r="F4">
-        <v>0.01722975568031216</v>
+        <v>0</v>
       </c>
       <c r="G4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4">
-        <v>0.03445951136062431</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -508,25 +508,25 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E5">
-        <v>-0.5137651821862349</v>
+        <v>-0.2212244897959184</v>
       </c>
       <c r="F5">
-        <v>0.0008220051984522333</v>
+        <v>0.122605933936797</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I5">
-        <v>0.003288020793808933</v>
+        <v>0.367817801810391</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -537,25 +537,25 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D6">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="F6">
+        <v>0.6056681466311387</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
         <v>20</v>
       </c>
-      <c r="E6">
-        <v>0.04360902255639097</v>
-      </c>
-      <c r="F6">
-        <v>0.8551479470173744</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
       <c r="I6">
-        <v>0.8551479470173744</v>
+        <v>0.876292262028499</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -566,25 +566,25 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E7">
-        <v>-0.08502024291497975</v>
+        <v>0.02282508201753031</v>
       </c>
       <c r="F7">
-        <v>0.6117949873302611</v>
+        <v>0.876292262028499</v>
       </c>
       <c r="G7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7">
-        <v>0.8157266497736814</v>
+        <v>0.876292262028499</v>
       </c>
     </row>
   </sheetData>
